--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-tiflow-op-accept-bundle.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-tiflow-op-accept-bundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4072" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4091" uniqueCount="354">
   <si>
     <t>Property</t>
   </si>
@@ -268,8 +268,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -384,6 +384,16 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -486,6 +496,9 @@
 This specification defines some specific uses of Bundle.link for [searching](http://hl7.org/fhir/R4/search.html#conformance) and [paging](http://hl7.org/fhir/R4/http.html#paging), but no specific uses for Bundle.entry.link, and no defined function in a transaction - the meaning is implementation specific.</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.id</t>
   </si>
   <si>
@@ -502,9 +515,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -525,6 +535,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -561,6 +581,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -568,6 +591,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -592,8 +618,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -642,6 +668,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -651,8 +680,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -708,8 +737,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -763,6 +792,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -790,8 +822,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -882,7 +914,7 @@
     <t>Bundle.entry:task.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Task {https://gematik.de/fhir/tiflow/StructureDefinition/ti-task}
+    <t xml:space="preserve">Task {https://gematik.de/fhir/tiflow/StructureDefinition/tiflow-order-task}
 </t>
   </si>
   <si>
@@ -992,25 +1024,6 @@
   </si>
   <si>
     <t>Bundle.entry:binary.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_PR_Binary}
-</t>
-  </si>
-  <si>
-    <t>Pure binary content defined by a format other than FHIR</t>
-  </si>
-  <si>
-    <t>A resource that represents the data of a single raw artifact as digital content accessible in its native format.  A Binary resource can contain any content, whether text, image, pdf, zip archive, etc.</t>
-  </si>
-  <si>
-    <t>Typically, Binary resources are used for handling content such as:  
-* CDA Documents (i.e. with XDS) 
-* PDF Documents 
-* Images (the Media resource is preferred for handling images, but not possible when the content is already binary - e.g. XDS).</t>
-  </si>
-  <si>
-    <t>ED</t>
   </si>
   <si>
     <t>Bundle.entry:binary.search</t>
@@ -1423,7 +1436,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="61.33203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="58.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1441,15 +1454,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.91015625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="22.78515625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2238,30 +2251,30 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2287,13 +2300,13 @@
         <v>108</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2301,7 +2314,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>78</v>
@@ -2319,13 +2332,13 @@
         <v>78</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>78</v>
@@ -2343,7 +2356,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>88</v>
@@ -2367,15 +2380,15 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2398,16 +2411,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2457,7 +2470,7 @@
         <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2478,18 +2491,18 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2512,16 +2525,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2571,7 +2584,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2580,7 +2593,7 @@
         <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>100</v>
@@ -2600,10 +2613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2626,16 +2639,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2685,7 +2698,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2694,7 +2707,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
@@ -2703,7 +2716,7 @@
         <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>78</v>
@@ -2714,10 +2727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2740,13 +2753,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2797,7 +2810,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2815,7 +2828,7 @@
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2826,14 +2839,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2852,16 +2865,16 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2899,19 +2912,19 @@
         <v>78</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2923,13 +2936,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -2940,14 +2953,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2966,19 +2979,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3027,7 +3040,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3039,7 +3052,7 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -3056,10 +3069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3082,15 +3095,17 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3139,7 +3154,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -3168,10 +3183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3197,12 +3212,14 @@
         <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3251,7 +3268,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3280,10 +3297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3291,10 +3308,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3306,13 +3323,13 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3351,19 +3368,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3372,16 +3389,16 @@
         <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3392,10 +3409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3418,13 +3435,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3475,7 +3492,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3493,7 +3510,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3504,14 +3521,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3530,16 +3547,16 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3577,19 +3594,19 @@
         <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3601,13 +3618,13 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3618,14 +3635,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3644,19 +3661,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3705,7 +3722,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3717,7 +3734,7 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3734,10 +3751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3763,10 +3780,10 @@
         <v>78</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3817,7 +3834,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3829,7 +3846,7 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
@@ -3846,10 +3863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3875,13 +3892,13 @@
         <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3931,7 +3948,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3960,10 +3977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3986,13 +4003,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4043,7 +4060,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4061,7 +4078,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4072,10 +4089,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4098,13 +4115,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4155,7 +4172,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4164,7 +4181,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4173,7 +4190,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4184,10 +4201,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4210,13 +4227,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4267,7 +4284,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4285,7 +4302,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4296,14 +4313,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4322,16 +4339,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4369,19 +4386,19 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4393,13 +4410,13 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4410,14 +4427,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4436,19 +4453,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4497,7 +4514,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4509,7 +4526,7 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4526,10 +4543,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4555,13 +4572,13 @@
         <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4587,13 +4604,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -4611,7 +4628,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4640,10 +4657,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4666,16 +4683,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4725,7 +4742,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4754,10 +4771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4780,13 +4797,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4837,7 +4854,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4846,7 +4863,7 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
@@ -4855,7 +4872,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -4866,10 +4883,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4892,13 +4909,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4949,7 +4966,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4967,7 +4984,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -4978,14 +4995,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5004,16 +5021,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5051,19 +5068,19 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5075,13 +5092,13 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5092,14 +5109,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5118,19 +5135,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5179,7 +5196,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5191,7 +5208,7 @@
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -5208,10 +5225,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5237,10 +5254,10 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5267,13 +5284,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5291,7 +5308,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5320,10 +5337,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5349,13 +5366,13 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5405,7 +5422,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5434,10 +5451,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5460,15 +5477,17 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5517,7 +5536,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5546,10 +5565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5572,15 +5591,17 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5629,7 +5650,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5658,10 +5679,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5684,15 +5705,17 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5741,7 +5764,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5770,10 +5793,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5796,15 +5819,17 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -5853,7 +5878,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5882,10 +5907,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5908,13 +5933,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5965,7 +5990,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -5974,7 +5999,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -5983,7 +6008,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -5994,10 +6019,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6020,13 +6045,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6077,7 +6102,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6095,7 +6120,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6106,14 +6131,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6132,16 +6157,16 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6179,19 +6204,19 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6203,13 +6228,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6220,14 +6245,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6246,19 +6271,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6307,7 +6332,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6319,7 +6344,7 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -6336,10 +6361,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6362,15 +6387,17 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6419,7 +6446,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6448,10 +6475,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6477,12 +6504,14 @@
         <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6531,7 +6560,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6560,10 +6589,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6586,16 +6615,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6645,7 +6674,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6674,10 +6703,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6700,16 +6729,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6759,7 +6788,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6788,10 +6817,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6814,16 +6843,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6873,7 +6902,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -6891,7 +6920,7 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -6902,13 +6931,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>78</v>
@@ -6930,13 +6959,13 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6987,7 +7016,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -6996,16 +7025,16 @@
         <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7016,10 +7045,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7042,13 +7071,13 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7099,7 +7128,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7117,7 +7146,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7128,14 +7157,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7154,16 +7183,16 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7201,19 +7230,19 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7225,13 +7254,13 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7242,14 +7271,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7268,19 +7297,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7329,7 +7358,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7341,7 +7370,7 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -7358,10 +7387,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7387,10 +7416,10 @@
         <v>81</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7441,7 +7470,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7453,7 +7482,7 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -7470,10 +7499,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7499,13 +7528,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7555,7 +7584,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7584,10 +7613,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7610,13 +7639,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7667,7 +7696,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7685,7 +7714,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -7696,10 +7725,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7722,13 +7751,13 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7779,7 +7808,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -7788,7 +7817,7 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
@@ -7797,7 +7826,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -7808,10 +7837,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7834,13 +7863,13 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7891,7 +7920,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -7909,7 +7938,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -7920,14 +7949,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7946,16 +7975,16 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7993,19 +8022,19 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8017,13 +8046,13 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8034,14 +8063,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8060,19 +8089,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8121,7 +8150,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8133,7 +8162,7 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8150,10 +8179,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8179,13 +8208,13 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8211,13 +8240,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8235,7 +8264,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8264,10 +8293,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8290,16 +8319,16 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8349,7 +8378,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8378,10 +8407,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8404,13 +8433,13 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8461,7 +8490,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8470,7 +8499,7 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>100</v>
@@ -8479,7 +8508,7 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -8490,10 +8519,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8516,13 +8545,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8573,7 +8602,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8591,7 +8620,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -8602,14 +8631,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8628,16 +8657,16 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8675,19 +8704,19 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -8699,13 +8728,13 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -8716,14 +8745,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8742,19 +8771,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -8803,7 +8832,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -8815,7 +8844,7 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -8832,10 +8861,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8861,10 +8890,10 @@
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8891,13 +8920,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -8915,7 +8944,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>88</v>
@@ -8944,10 +8973,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8973,13 +9002,13 @@
         <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9029,7 +9058,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>88</v>
@@ -9058,10 +9087,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9084,15 +9113,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9141,7 +9172,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9170,10 +9201,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9196,15 +9227,17 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9253,7 +9286,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9282,10 +9315,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9308,15 +9341,17 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -9365,7 +9400,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9394,10 +9429,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9420,15 +9455,17 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9477,7 +9514,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9506,10 +9543,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9532,13 +9569,13 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9589,7 +9626,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -9598,7 +9635,7 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
@@ -9607,7 +9644,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -9618,10 +9655,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9644,13 +9681,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9701,7 +9738,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -9719,7 +9756,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -9730,14 +9767,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9756,16 +9793,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9803,19 +9840,19 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -9827,13 +9864,13 @@
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -9844,14 +9881,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9870,19 +9907,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -9931,7 +9968,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -9943,7 +9980,7 @@
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -9960,10 +9997,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9986,15 +10023,17 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10043,7 +10082,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -10072,10 +10111,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10101,12 +10140,14 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10155,7 +10196,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10184,10 +10225,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10210,16 +10251,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10269,7 +10310,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10298,10 +10339,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10324,16 +10365,16 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10383,7 +10424,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10412,10 +10453,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10438,16 +10479,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10497,7 +10538,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -10515,7 +10556,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -10526,13 +10567,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>78</v>
@@ -10554,13 +10595,13 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10611,7 +10652,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -10620,16 +10661,16 @@
         <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -10640,10 +10681,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10666,13 +10707,13 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10723,7 +10764,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -10741,7 +10782,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -10752,14 +10793,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10778,16 +10819,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10825,19 +10866,19 @@
         <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -10849,13 +10890,13 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -10866,14 +10907,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10892,19 +10933,19 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -10953,7 +10994,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -10965,7 +11006,7 @@
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -10982,10 +11023,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11011,10 +11052,10 @@
         <v>81</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11065,7 +11106,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11077,7 +11118,7 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -11094,10 +11135,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11123,13 +11164,13 @@
         <v>102</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11179,7 +11220,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11208,10 +11249,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11231,20 +11272,18 @@
         <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>313</v>
+        <v>203</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -11293,7 +11332,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -11311,7 +11350,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>317</v>
+        <v>206</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -11322,10 +11361,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11348,13 +11387,13 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11405,7 +11444,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -11414,7 +11453,7 @@
         <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>100</v>
@@ -11423,7 +11462,7 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -11434,10 +11473,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11460,13 +11499,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11517,7 +11556,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -11535,7 +11574,7 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -11546,14 +11585,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11572,16 +11611,16 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11619,19 +11658,19 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -11643,13 +11682,13 @@
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -11660,14 +11699,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11686,19 +11725,19 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -11747,7 +11786,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -11759,7 +11798,7 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -11776,10 +11815,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11805,13 +11844,13 @@
         <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11837,13 +11876,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -11861,7 +11900,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -11890,10 +11929,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11916,16 +11955,16 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11975,7 +12014,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12004,10 +12043,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12030,13 +12069,13 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12087,7 +12126,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12096,7 +12135,7 @@
         <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>100</v>
@@ -12105,7 +12144,7 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12116,10 +12155,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12142,13 +12181,13 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12199,7 +12238,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12217,7 +12256,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12228,14 +12267,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12254,16 +12293,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12301,19 +12340,19 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -12325,13 +12364,13 @@
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -12342,14 +12381,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12368,19 +12407,19 @@
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -12429,7 +12468,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -12441,7 +12480,7 @@
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -12458,10 +12497,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12487,10 +12526,10 @@
         <v>108</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12517,13 +12556,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -12541,7 +12580,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>88</v>
@@ -12570,10 +12609,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12599,13 +12638,13 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12655,7 +12694,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>88</v>
@@ -12684,10 +12723,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12710,15 +12749,17 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -12767,7 +12808,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -12796,10 +12837,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12822,15 +12863,17 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -12879,7 +12922,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -12908,10 +12951,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12934,15 +12977,17 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -12991,7 +13036,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13020,10 +13065,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13046,15 +13091,17 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -13103,7 +13150,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13132,10 +13179,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13158,13 +13205,13 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13215,7 +13262,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -13224,7 +13271,7 @@
         <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>100</v>
@@ -13233,7 +13280,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13244,10 +13291,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13270,13 +13317,13 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13327,7 +13374,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -13345,7 +13392,7 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -13356,14 +13403,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13382,16 +13429,16 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13429,19 +13476,19 @@
         <v>78</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -13453,13 +13500,13 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -13470,14 +13517,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13496,19 +13543,19 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -13557,7 +13604,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -13569,7 +13616,7 @@
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
@@ -13586,10 +13633,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13612,15 +13659,17 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -13669,7 +13718,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -13698,10 +13747,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13727,12 +13776,14 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -13781,7 +13832,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -13810,10 +13861,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13836,16 +13887,16 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13895,7 +13946,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -13924,10 +13975,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13950,16 +14001,16 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14009,7 +14060,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14038,10 +14089,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14064,16 +14115,16 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14123,7 +14174,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -14141,7 +14192,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -14152,10 +14203,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14178,19 +14229,19 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -14239,7 +14290,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -14248,7 +14299,7 @@
         <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>100</v>
@@ -14257,7 +14308,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>

--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-tiflow-op-accept-bundle.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-tiflow-op-accept-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
